--- a/xls/quest_v2.xlsx
+++ b/xls/quest_v2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
   <si>
     <t>#</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,14 +68,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>與長老對話了解情況</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>前往黑森林，擊殺黑森林的野狼 ({current}/5)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>收集狼皮 ({current}/5)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -136,9 +128,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>talked_to_elder</t>
-  </si>
-  <si>
     <t>quest_reported</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -155,6 +144,34 @@
   </si>
   <si>
     <t>q_karen_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>與xi對話了解情況</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>action_complete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>action_start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set qk01_start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qk01_talk_xi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>//</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前往黑森林，擊殺黑森林的野狼 ({current}/{required})</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -360,7 +377,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -390,9 +407,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -718,49 +732,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="3.75" style="20" customWidth="1"/>
+    <col min="1" max="1" width="3.75" style="19" customWidth="1"/>
     <col min="2" max="2" width="21.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="26.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.375" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="16" t="s">
+      <c r="A1" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="19" t="s">
+      <c r="G1" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="18" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -778,160 +792,176 @@
       <c r="F2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="4" t="s">
         <v>5</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="31.5">
-      <c r="B3" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <v>100</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="12">
         <v>100</v>
       </c>
-      <c r="G3" s="15"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="14"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>32</v>
-      </c>
+      <c r="B6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="10"/>
     </row>
-    <row r="7" spans="1:9" ht="16.5">
+    <row r="7" spans="1:9" ht="31.5">
       <c r="B7" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
+      <c r="I7" s="10"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E8" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="11"/>
-    </row>
-    <row r="8" spans="1:9" ht="31.5">
-      <c r="B8" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>23</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H8" s="8">
         <v>5</v>
       </c>
-      <c r="I8" s="11"/>
+      <c r="I8" s="10"/>
     </row>
     <row r="9" spans="1:9">
+      <c r="A9" s="19" t="s">
+        <v>38</v>
+      </c>
       <c r="B9" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F9" s="8"/>
-      <c r="G9" s="8" t="s">
-        <v>29</v>
-      </c>
+      <c r="G9" s="8"/>
       <c r="H9" s="8">
-        <v>5</v>
-      </c>
-      <c r="I9" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="10"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="B10" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8">
-        <v>1</v>
-      </c>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="B11" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="13" t="s">
+      <c r="B10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="15"/>
+      <c r="F10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/xls/quest_v2.xlsx
+++ b/xls/quest_v2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
   <si>
     <t>#</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,38 +68,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>收集狼皮 ({current}/5)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用狼皮製作披風</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>回報任務</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>step_talk_elder</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>step_kill_wolves</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>step_collect_pelt</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>step_craft_cloak</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>step_report</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>kill</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -116,26 +84,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>craft</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>wolf</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>wolf_plet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>quest_reported</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>location</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>//</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -151,27 +103,94 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>action_complete</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>action_start</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>set qk01_start</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>qk01_talk_xi</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>//</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>前往黑森林，擊殺黑森林的野狼 ({current}/{required})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sword_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>收集刀子 ({current}/{required})</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>step_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>step_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>step_03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>step_05</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>step_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>step_02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>step_03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conds</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>actions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任務完成，跟 karen 回報任務</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qk01_report</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set qk01 done</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rm qk01_talk_xi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rm qk01_report ;
+set qk01 close ;
+complete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>actions_start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>actions_complete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set qk01_start ;
+set qk01 going</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -377,7 +396,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -437,6 +456,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -732,24 +754,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="3.75" style="19" customWidth="1"/>
     <col min="2" max="2" width="21.125" style="1" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="31.125" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.875" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" style="1" customWidth="1"/>
     <col min="9" max="9" width="16.375" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="1"/>
+    <col min="10" max="10" width="19.75" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="19" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>7</v>
@@ -767,13 +790,13 @@
         <v>9</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H1" s="18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
@@ -796,15 +819,15 @@
         <v>5</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="31.5">
+    <row r="3" spans="1:10" ht="31.5">
       <c r="B3" s="11" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>11</v>
@@ -819,12 +842,12 @@
         <v>100</v>
       </c>
       <c r="G3" s="12"/>
-      <c r="H3" s="12" t="s">
-        <v>36</v>
+      <c r="H3" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="I3" s="14"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="19" t="s">
         <v>0</v>
       </c>
@@ -844,124 +867,117 @@
         <v>9</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="6" t="s">
-        <v>29</v>
+      <c r="I5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="B6" s="7" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>22</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
-      <c r="I6" s="10"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="10" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="7" spans="1:9" ht="31.5">
+    <row r="7" spans="1:10" ht="31.5">
       <c r="B7" s="7" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="H7" s="8">
         <v>1</v>
       </c>
-      <c r="I7" s="10"/>
+      <c r="I7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J7" s="10"/>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="19" t="s">
-        <v>38</v>
-      </c>
+    <row r="8" spans="1:10">
       <c r="B8" s="7" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H8" s="8">
-        <v>5</v>
-      </c>
-      <c r="I8" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="8" t="s">
+    <row r="9" spans="1:10" ht="47.25">
+      <c r="B9" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8">
-        <v>1</v>
-      </c>
-      <c r="I9" s="10"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="B10" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="14"/>
+      <c r="C9" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>40</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/xls/quest_v2.xlsx
+++ b/xls/quest_v2.xlsx
@@ -175,22 +175,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>actions_start</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>actions_complete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>set qk01_start ;
+set qk01 going</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>rm qk01_report ;
 set qk01 close ;
-complete</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>actions_start</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>actions_complete</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>set qk01_start ;
-set qk01 going</t>
+close q_karen_01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -819,10 +819,10 @@
         <v>5</v>
       </c>
       <c r="H2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="31.5">
@@ -843,7 +843,7 @@
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I3" s="14"/>
     </row>
@@ -976,7 +976,7 @@
         <v>32</v>
       </c>
       <c r="J9" s="20" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/xls/quest_v2.xlsx
+++ b/xls/quest_v2.xlsx
@@ -766,7 +766,7 @@
     <col min="7" max="7" width="15.25" style="1" customWidth="1"/>
     <col min="8" max="8" width="18.875" style="1" customWidth="1"/>
     <col min="9" max="9" width="16.375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="19.75" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.25" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/xls/quest_v2.xlsx
+++ b/xls/quest_v2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="42">
   <si>
     <t>#</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -92,13 +92,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>q_karen_01</t>
-  </si>
-  <si>
-    <t>q_karen_01</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>與xi對話了解情況</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -156,14 +149,6 @@
   </si>
   <si>
     <t>任務完成，跟 karen 回報任務</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>flag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>qk01_report</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -188,9 +173,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>rm qk01_report ;
-set qk01 close ;
-close q_karen_01</t>
+    <t>QK01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QK01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>none</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -819,15 +810,15 @@
         <v>5</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="31.5">
       <c r="B3" s="11" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>11</v>
@@ -843,7 +834,7 @@
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="I3" s="14"/>
     </row>
@@ -873,44 +864,44 @@
         <v>10</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
       <c r="I6" s="8"/>
       <c r="J6" s="10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="31.5">
       <c r="B7" s="7" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>13</v>
@@ -923,61 +914,57 @@
         <v>1</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J7" s="10"/>
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="7" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H8" s="8">
         <v>1</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="47.25">
+    <row r="9" spans="1:10">
       <c r="B9" s="11" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>37</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F9" s="12"/>
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="20" t="s">
-        <v>43</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J9" s="20"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
